--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487732_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487732_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5591</v>
+        <v>6.0502</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4201</v>
+        <v>6.32</v>
       </c>
       <c r="F2" t="n">
-        <v>0.139</v>
+        <v>-0.2698</v>
       </c>
       <c r="G2" t="n">
         <v>1.8952</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3638</v>
+        <v>0.8549</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0565</v>
+        <v>0.9564</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3073</v>
+        <v>-0.1015</v>
       </c>
       <c r="V2" t="n">
         <v>1.5537</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7621</v>
+        <v>4.9167</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6941</v>
+        <v>5.7942</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>4.2118</v>
@@ -688,13 +688,13 @@
         <v>0.5821</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4975</v>
+        <v>-0.3429</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2053</v>
+        <v>-0.1052</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2923</v>
+        <v>-0.2378</v>
       </c>
       <c r="V3" t="n">
         <v>0.6597</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3371</v>
+        <v>4.3554</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1053</v>
+        <v>4.2054</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2317</v>
+        <v>0.15</v>
       </c>
       <c r="G4" t="n">
         <v>1.5672</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3818</v>
+        <v>0.4001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.498</v>
+        <v>0.5981</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1162</v>
+        <v>-0.1979</v>
       </c>
       <c r="V4" t="n">
         <v>1.2239</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4192</v>
+        <v>2.5089</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8138</v>
+        <v>4.7127</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3946</v>
+        <v>-2.2038</v>
       </c>
       <c r="G5" t="n">
         <v>0.7874</v>
@@ -844,13 +844,13 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7781</v>
+        <v>0.8678</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4517</v>
+        <v>1.3506</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6736</v>
+        <v>-0.4828</v>
       </c>
       <c r="V5" t="n">
         <v>0.6597</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7989</v>
+        <v>1.7716</v>
       </c>
       <c r="E6" t="n">
         <v>0.7133</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0856</v>
+        <v>1.0584</v>
       </c>
       <c r="G6" t="n">
         <v>0.7708</v>
@@ -922,13 +922,13 @@
         <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6496</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>-0.3387</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3109</v>
+        <v>-0.3381</v>
       </c>
       <c r="V6" t="n">
         <v>0.7075</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>M. ALONSO GONZÁLEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4457</v>
+        <v>-0.0056</v>
       </c>
       <c r="E7" t="n">
-        <v>0.619</v>
+        <v>0.0123</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1732</v>
+        <v>-0.0179</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.874</v>
+        <v>-0.2725</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.5987</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7246</v>
+        <v>-0.2725</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4969</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5653</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0684</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3771</v>
+        <v>-0.2725</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0333</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6562</v>
+        <v>-0.2725</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.1211</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7054</v>
+        <v>0.0123</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.62</v>
+        <v>-0.1335</v>
       </c>
       <c r="V7" t="n">
-        <v>2.0701</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4104</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ALONSO GONZÁLEZ</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0056</v>
+        <v>-0.0914</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0123</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0179</v>
+        <v>-0.0097</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2725</v>
+        <v>-2.874</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-3.5987</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2725</v>
+        <v>0.7246</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-1.4969</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1.5653</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0684</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2725</v>
+        <v>-1.3771</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-2.0333</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2725</v>
+        <v>0.6562</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1211</v>
+        <v>-0.4517</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0123</v>
+        <v>0.0047</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1335</v>
+        <v>-0.4564</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.0701</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4104</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4443</v>
+        <v>-0.8615</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9236</v>
+        <v>2.7244</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3679</v>
+        <v>-3.586</v>
       </c>
       <c r="G9" t="n">
         <v>0.4154</v>
@@ -1156,13 +1156,13 @@
         <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4134</v>
+        <v>0.1694</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.581</v>
+        <v>0.2198</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1676</v>
+        <v>-0.0504</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2821</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8685</v>
+        <v>-1.8413</v>
       </c>
       <c r="E10" t="n">
         <v>-1.516</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3525</v>
+        <v>-0.3253</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4157</v>
@@ -1234,13 +1234,13 @@
         <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9767</v>
+        <v>-0.9494</v>
       </c>
       <c r="T10" t="n">
         <v>-0.5328000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4439</v>
+        <v>-0.4166</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2821</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8098</v>
+        <v>-2.9655</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5336</v>
+        <v>0.1952</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2762</v>
+        <v>-3.1607</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.415</v>
+        <v>-1.9177</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6129</v>
+        <v>-2.4683</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1979</v>
+        <v>0.5506</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0483</v>
+        <v>0.7762</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0329</v>
+        <v>-1.1369</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08119999999999999</v>
+        <v>1.9131</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4633</v>
+        <v>-2.6939</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.58</v>
+        <v>-1.3314</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1168</v>
+        <v>-1.3625</v>
       </c>
       <c r="P11" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R11" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2008</v>
+        <v>0.2641</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.3892</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5592</v>
+        <v>-0.125</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2239</v>
+        <v>-1.506</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2239</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0116</v>
+        <v>-3.6552</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6056</v>
+        <v>-2.4335</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.406</v>
+        <v>-1.2217</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9177</v>
+        <v>-0.415</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4683</v>
+        <v>-0.6129</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5506</v>
+        <v>0.1979</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7762</v>
+        <v>0.0483</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1369</v>
+        <v>-0.0329</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9131</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6939</v>
+        <v>-0.4633</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3314</v>
+        <v>-0.58</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3625</v>
+        <v>0.1168</v>
       </c>
       <c r="P12" t="n">
-        <v>0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.782</v>
+        <v>-1.0461</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4116</v>
+        <v>-0.5415</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3703</v>
+        <v>-0.5047</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.506</v>
+        <v>-1.2239</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.506</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="13">
@@ -1468,13 +1468,13 @@
         <v>13.5824</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0319</v>
+        <v>-1.0318</v>
       </c>
       <c r="T13" t="n">
         <v>2.0129</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.045</v>
+        <v>-3.0447</v>
       </c>
       <c r="V13" t="n">
         <v>3.580499999999999</v>
@@ -1483,7 +1483,7 @@
         <v>8.376000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.7955</v>
+        <v>-4.795500000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9502</v>
+        <v>5.0569</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0549</v>
+        <v>4.7556</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1047</v>
+        <v>0.3013</v>
       </c>
       <c r="G14" t="n">
         <v>2.8808</v>
@@ -1546,13 +1546,13 @@
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9455</v>
+        <v>0.1612</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5933</v>
+        <v>0.1074</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3522</v>
+        <v>0.0538</v>
       </c>
       <c r="V14" t="n">
         <v>2.9851</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3043</v>
+        <v>2.2977</v>
       </c>
       <c r="E15" t="n">
-        <v>5.796</v>
+        <v>4.795</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4917</v>
+        <v>-2.4973</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0092</v>
@@ -1624,13 +1624,13 @@
         <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5718</v>
+        <v>1.5651</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9066</v>
+        <v>0.9056</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6651</v>
+        <v>0.6595</v>
       </c>
       <c r="V15" t="n">
         <v>0.1597</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9322</v>
+        <v>1.8471</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4405</v>
+        <v>1.1402</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4916</v>
+        <v>0.7069</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3777</v>
@@ -1702,13 +1702,13 @@
         <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>1.268</v>
+        <v>1.183</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0442</v>
+        <v>0.7439</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2239</v>
+        <v>0.4391</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1224</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3313</v>
+        <v>0.2341</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8231</v>
+        <v>4.4803</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1545</v>
+        <v>-4.2463</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4664</v>
+        <v>2.8729</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0437</v>
+        <v>4.0436</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4227</v>
+        <v>-1.1707</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9479</v>
+        <v>6.0181</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1359</v>
+        <v>4.5972</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8119</v>
+        <v>1.4209</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4142</v>
+        <v>-3.1452</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1796</v>
+        <v>-0.5537</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2346</v>
+        <v>-2.5916</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3582</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6126</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.923</v>
+        <v>-0.1139</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3104</v>
+        <v>-0.4593</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8358</v>
+        <v>-0.7075</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0478</v>
+        <v>0.5164</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.788</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4379</v>
+        <v>-0.2039</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5961</v>
+        <v>1.6903</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1582</v>
+        <v>-1.8942</v>
       </c>
       <c r="G18" t="n">
-        <v>0.21</v>
+        <v>-0.9179</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9717</v>
+        <v>0.1087</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.7617</v>
+        <v>-1.0266</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7514</v>
+        <v>1.4708</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6899</v>
+        <v>0.8568</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9386</v>
+        <v>0.614</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5413</v>
+        <v>-2.3887</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2817</v>
+        <v>-0.7481</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-1.6406</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3582</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1521</v>
+        <v>0.6006</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3481</v>
+        <v>0.3718</v>
       </c>
       <c r="U18" t="n">
-        <v>0.804</v>
+        <v>0.2288</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4418</v>
+        <v>1.6656</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7553</v>
+        <v>1.788</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6866</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8487</v>
+        <v>-0.5376</v>
       </c>
       <c r="E19" t="n">
-        <v>3.8797</v>
+        <v>1.3226</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.7284</v>
+        <v>-1.8603</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8729</v>
+        <v>-0.4664</v>
       </c>
       <c r="H19" t="n">
-        <v>4.0436</v>
+        <v>-0.0437</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1707</v>
+        <v>-0.4227</v>
       </c>
       <c r="J19" t="n">
-        <v>6.0181</v>
+        <v>0.9479</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5972</v>
+        <v>0.1359</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4209</v>
+        <v>0.8119</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1452</v>
+        <v>-1.4142</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5537</v>
+        <v>-0.1796</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.5916</v>
+        <v>-1.2346</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3582</v>
+        <v>1.3582</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6559</v>
+        <v>0.4063</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7145</v>
+        <v>0.4225</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9414</v>
+        <v>-0.0162</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7075</v>
+        <v>-1.8358</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5164</v>
+        <v>-0.0478</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0958</v>
+        <v>-1.1197</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0897</v>
+        <v>2.2645</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1856</v>
+        <v>-3.3842</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9179</v>
+        <v>0.7433</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1087</v>
+        <v>0.3485</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0266</v>
+        <v>0.3948</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4708</v>
+        <v>3.0309</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8568</v>
+        <v>1.001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.614</v>
+        <v>2.0298</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3887</v>
+        <v>-2.2875</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7481</v>
+        <v>-0.6525</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6406</v>
+        <v>-1.635</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2914</v>
+        <v>-0.4153</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2288</v>
+        <v>0.2038</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0625</v>
+        <v>-0.6191</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6656</v>
+        <v>-1.8358</v>
       </c>
       <c r="W20" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1224</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2621</v>
+        <v>-1.4107</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3646</v>
+        <v>-1.3969</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6267</v>
+        <v>-0.0138</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7433</v>
+        <v>0.21</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3485</v>
+        <v>2.9717</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3948</v>
+        <v>-2.7617</v>
       </c>
       <c r="J21" t="n">
-        <v>3.0309</v>
+        <v>0.7514</v>
       </c>
       <c r="K21" t="n">
-        <v>1.001</v>
+        <v>2.6899</v>
       </c>
       <c r="L21" t="n">
-        <v>2.0298</v>
+        <v>-1.9386</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2875</v>
+        <v>-0.5413</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6525</v>
+        <v>0.2817</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.635</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3881</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5576</v>
+        <v>1.1793</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3039</v>
+        <v>0.5473</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8616</v>
+        <v>0.632</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8358</v>
+        <v>-1.4418</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7553</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8358</v>
+        <v>-0.6866</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2342</v>
+        <v>-3.846</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7162</v>
+        <v>-3.516</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.518</v>
+        <v>-0.3301</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3908</v>
@@ -2170,13 +2170,13 @@
         <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4852</v>
+        <v>-0.097</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2905</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1947</v>
+        <v>-0.0067</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.1589</v>
+        <v>-9.8309</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6724</v>
+        <v>-5.0718</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.4865</v>
+        <v>-4.7591</v>
       </c>
       <c r="G23" t="n">
         <v>-6.298</v>
@@ -2248,13 +2248,13 @@
         <v>0.194</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.637</v>
+        <v>-0.309</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6539</v>
+        <v>-0.0533</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9832</v>
+        <v>-0.2557</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4477</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.1822</v>
+        <v>-7.513</v>
       </c>
       <c r="E24" t="n">
         <v>10.4638</v>
       </c>
       <c r="F24" t="n">
-        <v>-20.6463</v>
+        <v>-17.9771</v>
       </c>
       <c r="G24" t="n">
         <v>-3.753000000000001</v>
@@ -2326,16 +2326,16 @@
         <v>9.701600000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0319</v>
+        <v>3.701099999999999</v>
       </c>
       <c r="T24" t="n">
         <v>3.0448</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.013</v>
+        <v>0.6561999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.580600000000001</v>
+        <v>-3.5806</v>
       </c>
       <c r="W24" t="n">
         <v>4.7953</v>
